--- a/data/trans_camb/IP1005-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP1005-Edad-trans_camb.xlsx
@@ -636,7 +636,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,4</t>
+          <t>0,0; 2,99</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -656,7 +656,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,51</t>
+          <t>0,0; 1,52</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 1,17</t>
+          <t>-0,51; 1,26</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 1,45</t>
+          <t>-0,51; 1,44</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,82; 0,25</t>
+          <t>-1,8; 0,26</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 1,48</t>
+          <t>-1,07; 1,58</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 0,45</t>
+          <t>-0,88; 0,45</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 0,99</t>
+          <t>-0,54; 1,07</t>
         </is>
       </c>
     </row>
@@ -878,17 +878,17 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
+          <t>-88,33; —</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>-100,0; —</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-81,23; 750,4</t>
+          <t>-76,19; 643,55</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,65; 0,73</t>
+          <t>-2,64; 0,8</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,56; 0,25</t>
+          <t>-3,07; 0,25</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,13</t>
+          <t>0,0; 2,16</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,74</t>
+          <t>0,0; 1,51</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 0,64</t>
+          <t>-1,0; 0,85</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 0,45</t>
+          <t>-1,05; 0,47</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,05</t>
+          <t>0,0; 2,07</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,19</t>
+          <t>0,0; 1,03</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 0,39</t>
+          <t>-0,51; 0,38</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 0,5</t>
+          <t>-0,41; 0,51</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,56; 0,27</t>
+          <t>-0,47; 0,28</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,22; 0,88</t>
+          <t>-0,22; 0,83</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 0,23</t>
+          <t>-0,39; 0,18</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,19; 0,51</t>
+          <t>-0,19; 0,49</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-89,34; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -1346,17 +1346,17 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-68,2; —</t>
+          <t>-73,1; —</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-83,3; 236,25</t>
+          <t>-83,34; 171,45</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-48,43; 407,83</t>
+          <t>-47,05; 370,12</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP1005-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP1005-Edad-trans_camb.xlsx
@@ -636,7 +636,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,99</t>
+          <t>0,0; 2,97</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -656,7 +656,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,52</t>
+          <t>0,0; 1,48</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 1,26</t>
+          <t>-0,5; 1,17</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 1,44</t>
+          <t>-0,51; 1,45</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,8; 0,26</t>
+          <t>-1,82; 0,27</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,07; 1,58</t>
+          <t>-1,11; 1,42</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 0,45</t>
+          <t>-0,92; 0,46</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 1,07</t>
+          <t>-0,49; 1,0</t>
         </is>
       </c>
     </row>
@@ -878,17 +878,17 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-88,33; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-76,19; 643,55</t>
+          <t>-75,0; 610,77</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,64; 0,8</t>
+          <t>-2,68; 0,78</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,07; 0,25</t>
+          <t>-3,08; 0,25</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,16</t>
+          <t>0,0; 2,45</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,51</t>
+          <t>0,0; 1,71</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,0; 0,85</t>
+          <t>-1,16; 0,65</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 0,47</t>
+          <t>-1,13; 0,47</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,07</t>
+          <t>0,0; 2,46</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,03</t>
+          <t>0,0; 1,13</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 0,38</t>
+          <t>-0,5; 0,37</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,41; 0,51</t>
+          <t>-0,41; 0,55</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 0,28</t>
+          <t>-0,48; 0,27</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,22; 0,83</t>
+          <t>-0,22; 0,82</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 0,18</t>
+          <t>-0,38; 0,22</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,19; 0,49</t>
+          <t>-0,22; 0,48</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -1346,17 +1346,17 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-73,1; —</t>
+          <t>-73,89; 1195,53</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-83,34; 171,45</t>
+          <t>-83,73; 231,72</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-47,05; 370,12</t>
+          <t>-56,44; 340,48</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP1005-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP1005-Edad-trans_camb.xlsx
@@ -519,13 +519,13 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="F1" s="3" t="n"/>
@@ -598,17 +598,17 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>0,82</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -636,7 +636,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,97</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -646,7 +646,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 3,4</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -656,7 +656,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,48</t>
+          <t>0,0; 1,51</t>
         </is>
       </c>
     </row>
@@ -674,17 +674,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>inf%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -749,22 +749,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-0,53</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0,19</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>0,23</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>0,11</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-0,53</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0,19</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 1,17</t>
+          <t>-1,82; 0,25</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
+          <t>-1,05; 1,48</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>-0,51; 1,17</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
           <t>-0,51; 1,45</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-1,82; 0,27</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-1,11; 1,42</t>
-        </is>
-      </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 0,46</t>
+          <t>-0,86; 0,45</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 1,0</t>
+          <t>-0,62; 0,99</t>
         </is>
       </c>
     </row>
@@ -825,22 +825,22 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-67,8%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>24,6%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>91,23%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>42,29%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-67,8%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>24,6%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -868,7 +868,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-75,0; 610,77</t>
+          <t>-81,23; 750,4</t>
         </is>
       </c>
     </row>
@@ -905,22 +905,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>0,43</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0,34</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
           <t>-0,6</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>-0,77</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>0,43</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>0,34</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,68; 0,78</t>
+          <t>0,0; 2,13</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,08; 0,25</t>
+          <t>0,0; 1,74</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,45</t>
+          <t>-2,65; 0,73</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,71</t>
+          <t>-3,56; 0,25</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 0,65</t>
+          <t>-1,22; 0,64</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 0,47</t>
+          <t>-1,22; 0,45</t>
         </is>
       </c>
     </row>
@@ -981,22 +981,22 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
           <t>-58,33%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>-75,25%</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1066,17 +1066,17 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
+          <t>0,41</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>0,41</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 2,05</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1114,7 +1114,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,46</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,13</t>
+          <t>0,0; 1,19</t>
         </is>
       </c>
     </row>
@@ -1142,17 +1142,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1217,22 +1217,22 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>-0,09</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>0,25</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
           <t>-0,03</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>0,04</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>-0,09</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>0,25</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 0,37</t>
+          <t>-0,56; 0,27</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,41; 0,55</t>
+          <t>-0,22; 0,88</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 0,27</t>
+          <t>-0,48; 0,39</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,22; 0,82</t>
+          <t>-0,42; 0,5</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 0,22</t>
+          <t>-0,35; 0,23</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,22; 0,48</t>
+          <t>-0,19; 0,51</t>
         </is>
       </c>
     </row>
@@ -1293,22 +1293,22 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>-34,16%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>89,61%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
           <t>-11,12%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>15,1%</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>-34,16%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>89,61%</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-68,2; —</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -1346,17 +1346,17 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-73,89; 1195,53</t>
+          <t>-89,34; —</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-83,73; 231,72</t>
+          <t>-83,3; 236,25</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-56,44; 340,48</t>
+          <t>-48,43; 407,83</t>
         </is>
       </c>
     </row>
